--- a/artfynd/A 25701-2025 artfynd.xlsx
+++ b/artfynd/A 25701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017506</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25701-2025 artfynd.xlsx
+++ b/artfynd/A 25701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017506</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25701-2025 artfynd.xlsx
+++ b/artfynd/A 25701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017506</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25701-2025 artfynd.xlsx
+++ b/artfynd/A 25701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017506</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25701-2025 artfynd.xlsx
+++ b/artfynd/A 25701-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126017506</v>
+        <v>120415667</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>56338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100127</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Salmo trutta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödingsträsk, Nb</t>
+          <t>Varvlidbäcken 1, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>757495</v>
+        <v>756995</v>
       </c>
       <c r="R2" t="n">
-        <v>7324100</v>
+        <v>7324351</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Samexistens öring och bäckröding. Projekt invasiva fiskarter, Länsstyrelsen Norrbotten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,21 +768,132 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Andreas Broman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Andreas Broman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Invasiva fiskarter i Norrbotten</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126017506</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rödingsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>757495</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7324100</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25701-2025 artfynd.xlsx
+++ b/artfynd/A 25701-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017506</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Invasiva fiskarter i Norrbotten</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120415667</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>